--- a/artfynd/A 25259-2025 artfynd.xlsx
+++ b/artfynd/A 25259-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017276</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017275</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25259-2025 artfynd.xlsx
+++ b/artfynd/A 25259-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017276</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017275</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25259-2025 artfynd.xlsx
+++ b/artfynd/A 25259-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017276</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017275</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25259-2025 artfynd.xlsx
+++ b/artfynd/A 25259-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017276</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017275</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
